--- a/Siembra Ciclos Grupo ZP.xlsx
+++ b/Siembra Ciclos Grupo ZP.xlsx
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ignag\Desktop\HTML PARA DB DA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EE6FC03B-EEDF-4168-BE51-D8D0B341FA2B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5431C647-D323-457C-88CB-330481DD7B4A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="38640" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Relacion analiticas vs fincas" sheetId="2" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Relacion analiticas vs fincas'!$A$1:$F$151</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Relacion analiticas vs fincas'!$A$1:$F$152</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="754" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="758" uniqueCount="92">
   <si>
     <t>Cuenta Analitica en Recibo de Pago</t>
   </si>
@@ -685,7 +685,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{35372E75-D8AE-4D2B-8467-46A14CD55223}">
   <sheetPr codeName="Hoja1"/>
-  <dimension ref="A1:F151"/>
+  <dimension ref="A1:F152"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="34.21875" style="2" customWidth="1"/>
@@ -2998,19 +2998,22 @@
     </row>
     <row r="126" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A126" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="B126" s="2" t="s">
-        <v>30</v>
+        <v>90</v>
+      </c>
+      <c r="B126" s="2">
+        <v>2026</v>
       </c>
       <c r="C126" s="2" t="s">
         <v>22</v>
       </c>
       <c r="D126" s="2" t="s">
-        <v>86</v>
+        <v>23</v>
       </c>
       <c r="E126" s="2" t="s">
-        <v>50</v>
+        <v>42</v>
+      </c>
+      <c r="F126" s="2">
+        <v>1</v>
       </c>
     </row>
     <row r="127" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -3018,7 +3021,7 @@
         <v>7</v>
       </c>
       <c r="B127" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C127" s="2" t="s">
         <v>22</v>
@@ -3027,7 +3030,7 @@
         <v>86</v>
       </c>
       <c r="E127" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="128" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -3035,7 +3038,7 @@
         <v>7</v>
       </c>
       <c r="B128" s="2" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C128" s="2" t="s">
         <v>22</v>
@@ -3044,24 +3047,24 @@
         <v>86</v>
       </c>
       <c r="E128" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="129" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A129" s="2" t="s">
-        <v>32</v>
+        <v>7</v>
       </c>
       <c r="B129" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C129" s="2" t="s">
         <v>22</v>
       </c>
       <c r="D129" s="2" t="s">
-        <v>32</v>
+        <v>86</v>
       </c>
       <c r="E129" s="2" t="s">
-        <v>73</v>
+        <v>52</v>
       </c>
     </row>
     <row r="130" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -3078,7 +3081,7 @@
         <v>32</v>
       </c>
       <c r="E130" s="2" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="131" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -3095,55 +3098,55 @@
         <v>32</v>
       </c>
       <c r="E131" s="2" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="132" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A132" s="2" t="s">
-        <v>13</v>
+        <v>32</v>
       </c>
       <c r="B132" s="2" t="s">
-        <v>13</v>
+        <v>32</v>
       </c>
       <c r="C132" s="2" t="s">
         <v>22</v>
       </c>
       <c r="D132" s="2" t="s">
-        <v>13</v>
+        <v>32</v>
       </c>
       <c r="E132" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="133" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A133" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B133" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C133" s="2" t="s">
         <v>22</v>
       </c>
       <c r="D133" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E133" s="2" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="134" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A134" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B134" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C134" s="2" t="s">
         <v>22</v>
       </c>
       <c r="D134" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E134" s="2" t="s">
         <v>77</v>
@@ -3151,53 +3154,53 @@
     </row>
     <row r="135" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A135" s="2" t="s">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="B135" s="2" t="s">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="C135" s="2" t="s">
         <v>22</v>
       </c>
       <c r="D135" s="2" t="s">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="E135" s="2" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="136" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A136" s="2" t="s">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="B136" s="2" t="s">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="C136" s="2" t="s">
         <v>22</v>
       </c>
       <c r="D136" s="2" t="s">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="E136" s="2" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="137" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A137" s="2" t="s">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="B137" s="2" t="s">
-        <v>30</v>
+        <v>13</v>
       </c>
       <c r="C137" s="2" t="s">
         <v>22</v>
       </c>
       <c r="D137" s="2" t="s">
-        <v>32</v>
+        <v>13</v>
       </c>
       <c r="E137" s="2" t="s">
-        <v>43</v>
+        <v>79</v>
       </c>
     </row>
     <row r="138" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -3205,7 +3208,7 @@
         <v>3</v>
       </c>
       <c r="B138" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C138" s="2" t="s">
         <v>22</v>
@@ -3214,7 +3217,7 @@
         <v>32</v>
       </c>
       <c r="E138" s="2" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
     </row>
     <row r="139" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -3222,7 +3225,7 @@
         <v>3</v>
       </c>
       <c r="B139" s="2" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C139" s="2" t="s">
         <v>22</v>
@@ -3231,38 +3234,38 @@
         <v>32</v>
       </c>
       <c r="E139" s="2" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
     </row>
     <row r="140" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A140" s="2" t="s">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="B140" s="2" t="s">
-        <v>12</v>
+        <v>31</v>
       </c>
       <c r="C140" s="2" t="s">
         <v>22</v>
       </c>
       <c r="D140" s="2" t="s">
-        <v>12</v>
+        <v>32</v>
       </c>
       <c r="E140" s="2" t="s">
-        <v>80</v>
+        <v>44</v>
       </c>
     </row>
     <row r="141" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A141" s="2" t="s">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="B141" s="2" t="s">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="C141" s="2" t="s">
         <v>22</v>
       </c>
       <c r="D141" s="2" t="s">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="E141" s="2" t="s">
         <v>80</v>
@@ -3270,16 +3273,16 @@
     </row>
     <row r="142" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A142" s="2" t="s">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="B142" s="2" t="s">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="C142" s="2" t="s">
         <v>22</v>
       </c>
       <c r="D142" s="2" t="s">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="E142" s="2" t="s">
         <v>80</v>
@@ -3287,16 +3290,16 @@
     </row>
     <row r="143" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A143" s="2" t="s">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="B143" s="2" t="s">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="C143" s="2" t="s">
         <v>22</v>
       </c>
       <c r="D143" s="2" t="s">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="E143" s="2" t="s">
         <v>80</v>
@@ -3304,16 +3307,16 @@
     </row>
     <row r="144" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A144" s="2" t="s">
-        <v>55</v>
+        <v>4</v>
       </c>
       <c r="B144" s="2" t="s">
-        <v>55</v>
+        <v>4</v>
       </c>
       <c r="C144" s="2" t="s">
         <v>22</v>
       </c>
       <c r="D144" s="2" t="s">
-        <v>55</v>
+        <v>4</v>
       </c>
       <c r="E144" s="2" t="s">
         <v>80</v>
@@ -3321,33 +3324,33 @@
     </row>
     <row r="145" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A145" s="2" t="s">
-        <v>12</v>
+        <v>55</v>
       </c>
       <c r="B145" s="2" t="s">
-        <v>12</v>
+        <v>55</v>
       </c>
       <c r="C145" s="2" t="s">
         <v>22</v>
       </c>
       <c r="D145" s="2" t="s">
-        <v>12</v>
+        <v>55</v>
       </c>
       <c r="E145" s="2" t="s">
-        <v>45</v>
+        <v>80</v>
       </c>
     </row>
     <row r="146" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A146" s="2" t="s">
-        <v>66</v>
+        <v>12</v>
       </c>
       <c r="B146" s="2" t="s">
-        <v>66</v>
+        <v>12</v>
       </c>
       <c r="C146" s="2" t="s">
         <v>22</v>
       </c>
       <c r="D146" s="2" t="s">
-        <v>66</v>
+        <v>12</v>
       </c>
       <c r="E146" s="2" t="s">
         <v>45</v>
@@ -3355,16 +3358,16 @@
     </row>
     <row r="147" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A147" s="2" t="s">
-        <v>24</v>
+        <v>66</v>
       </c>
       <c r="B147" s="2" t="s">
-        <v>24</v>
+        <v>66</v>
       </c>
       <c r="C147" s="2" t="s">
         <v>22</v>
       </c>
       <c r="D147" s="2" t="s">
-        <v>24</v>
+        <v>66</v>
       </c>
       <c r="E147" s="2" t="s">
         <v>45</v>
@@ -3372,16 +3375,16 @@
     </row>
     <row r="148" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A148" s="2" t="s">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="B148" s="2" t="s">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="C148" s="2" t="s">
         <v>22</v>
       </c>
       <c r="D148" s="2" t="s">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="E148" s="2" t="s">
         <v>45</v>
@@ -3389,16 +3392,16 @@
     </row>
     <row r="149" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A149" s="2" t="s">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="B149" s="2" t="s">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="C149" s="2" t="s">
         <v>22</v>
       </c>
       <c r="D149" s="2" t="s">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="E149" s="2" t="s">
         <v>45</v>
@@ -3406,16 +3409,16 @@
     </row>
     <row r="150" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A150" s="2" t="s">
-        <v>19</v>
+        <v>4</v>
       </c>
       <c r="B150" s="2" t="s">
-        <v>30</v>
+        <v>4</v>
       </c>
       <c r="C150" s="2" t="s">
         <v>22</v>
       </c>
       <c r="D150" s="2" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E150" s="2" t="s">
         <v>45</v>
@@ -3426,7 +3429,7 @@
         <v>19</v>
       </c>
       <c r="B151" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C151" s="2" t="s">
         <v>22</v>
@@ -3435,17 +3438,34 @@
         <v>5</v>
       </c>
       <c r="E151" s="2" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="152" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A152" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B152" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="C152" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="D152" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="E152" s="2" t="s">
         <v>38</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F151" xr:uid="{35372E75-D8AE-4D2B-8467-46A14CD55223}">
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:F151">
-      <sortCondition ref="E2:E151"/>
+  <autoFilter ref="A1:F152" xr:uid="{35372E75-D8AE-4D2B-8467-46A14CD55223}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:F152">
+      <sortCondition ref="E2:E152"/>
     </sortState>
   </autoFilter>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:F151">
-    <sortCondition ref="E2:E151"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:F152">
+    <sortCondition ref="E2:E152"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Siembra Ciclos Grupo ZP.xlsx
+++ b/Siembra Ciclos Grupo ZP.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ignag\Desktop\HTML PARA DB DA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5431C647-D323-457C-88CB-330481DD7B4A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{34D422A0-91E8-4B3F-8D33-E1DBE8F1F088}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="38640" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Relacion analiticas vs fincas" sheetId="2" r:id="rId1"/>
@@ -2973,7 +2973,7 @@
         <v>42</v>
       </c>
       <c r="F124" s="2">
-        <v>1</v>
+        <v>29</v>
       </c>
     </row>
     <row r="125" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">

--- a/Siembra Ciclos Grupo ZP.xlsx
+++ b/Siembra Ciclos Grupo ZP.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ignag\Desktop\HTML PARA DB DA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{34D422A0-91E8-4B3F-8D33-E1DBE8F1F088}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D1038D5-B2B4-4C96-AF85-E620BA56EC3A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="38640" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Relacion analiticas vs fincas" sheetId="2" r:id="rId1"/>
@@ -2973,7 +2973,7 @@
         <v>42</v>
       </c>
       <c r="F124" s="2">
-        <v>29</v>
+        <v>66.5</v>
       </c>
     </row>
     <row r="125" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">

--- a/Siembra Ciclos Grupo ZP.xlsx
+++ b/Siembra Ciclos Grupo ZP.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ignag\Desktop\HTML PARA DB DA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D1038D5-B2B4-4C96-AF85-E620BA56EC3A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8E2E96BC-F6EE-447C-B87F-F5486BF48B11}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -688,8 +688,8 @@
   <dimension ref="A1:F152"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="34.21875" style="2" customWidth="1"/>
-    <col min="2" max="2" width="25.109375" style="2" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="25.77734375" style="2" customWidth="1"/>
+    <col min="2" max="2" width="17" style="2" customWidth="1"/>
     <col min="3" max="3" width="13" style="2" customWidth="1"/>
     <col min="4" max="4" width="40.5546875" style="2" customWidth="1"/>
     <col min="5" max="5" width="20.44140625" style="2" bestFit="1" customWidth="1"/>
@@ -2736,7 +2736,7 @@
         <v>41</v>
       </c>
       <c r="F112" s="2">
-        <v>0</v>
+        <v>483</v>
       </c>
     </row>
     <row r="113" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">

--- a/Siembra Ciclos Grupo ZP.xlsx
+++ b/Siembra Ciclos Grupo ZP.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ignag\Desktop\HTML PARA DB DA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8E2E96BC-F6EE-447C-B87F-F5486BF48B11}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{04770195-B142-4D8F-BEEA-BED78C7EC29D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Relacion analiticas vs fincas" sheetId="2" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Relacion analiticas vs fincas'!$A$1:$F$152</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Relacion analiticas vs fincas'!$A$1:$F$153</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="758" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="762" uniqueCount="93">
   <si>
     <t>Cuenta Analitica en Recibo de Pago</t>
   </si>
@@ -312,6 +312,9 @@
   </si>
   <si>
     <t>[MANI] Mani Rancho Pando</t>
+  </si>
+  <si>
+    <t>[MANI] Paraiso</t>
   </si>
 </sst>
 </file>
@@ -685,7 +688,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{35372E75-D8AE-4D2B-8467-46A14CD55223}">
   <sheetPr codeName="Hoja1"/>
-  <dimension ref="A1:F152"/>
+  <dimension ref="A1:F153"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="25.77734375" style="2" customWidth="1"/>
@@ -2761,10 +2764,10 @@
     </row>
     <row r="114" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A114" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="B114" s="2" t="s">
-        <v>4</v>
+        <v>92</v>
+      </c>
+      <c r="B114" s="2">
+        <v>2024</v>
       </c>
       <c r="C114" s="2" t="s">
         <v>22</v>
@@ -2781,30 +2784,30 @@
     </row>
     <row r="115" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A115" s="2" t="s">
-        <v>91</v>
+        <v>4</v>
       </c>
       <c r="B115" s="2" t="s">
-        <v>30</v>
+        <v>4</v>
       </c>
       <c r="C115" s="2" t="s">
         <v>22</v>
       </c>
       <c r="D115" s="2" t="s">
-        <v>55</v>
+        <v>4</v>
       </c>
       <c r="E115" s="2" t="s">
         <v>41</v>
       </c>
       <c r="F115" s="2">
-        <v>0</v>
+        <v>66</v>
       </c>
     </row>
     <row r="116" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A116" s="2" t="s">
-        <v>55</v>
+        <v>91</v>
       </c>
       <c r="B116" s="2" t="s">
-        <v>55</v>
+        <v>30</v>
       </c>
       <c r="C116" s="2" t="s">
         <v>22</v>
@@ -2821,44 +2824,44 @@
     </row>
     <row r="117" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A117" s="2" t="s">
-        <v>32</v>
+        <v>55</v>
       </c>
       <c r="B117" s="2" t="s">
-        <v>32</v>
+        <v>55</v>
       </c>
       <c r="C117" s="2" t="s">
         <v>22</v>
       </c>
       <c r="D117" s="2" t="s">
-        <v>32</v>
+        <v>55</v>
       </c>
       <c r="E117" s="2" t="s">
         <v>41</v>
       </c>
+      <c r="F117" s="2">
+        <v>159</v>
+      </c>
     </row>
     <row r="118" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A118" s="2" t="s">
-        <v>89</v>
+        <v>32</v>
       </c>
       <c r="B118" s="2" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="C118" s="2" t="s">
         <v>22</v>
       </c>
       <c r="D118" s="2" t="s">
-        <v>12</v>
+        <v>32</v>
       </c>
       <c r="E118" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="F118" s="2">
-        <v>0</v>
+        <v>41</v>
       </c>
     </row>
     <row r="119" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A119" s="2" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B119" s="2" t="s">
         <v>29</v>
@@ -2867,7 +2870,7 @@
         <v>22</v>
       </c>
       <c r="D119" s="2" t="s">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="E119" s="2" t="s">
         <v>36</v>
@@ -2878,7 +2881,7 @@
     </row>
     <row r="120" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A120" s="2" t="s">
-        <v>20</v>
+        <v>90</v>
       </c>
       <c r="B120" s="2" t="s">
         <v>29</v>
@@ -2887,18 +2890,18 @@
         <v>22</v>
       </c>
       <c r="D120" s="2" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="E120" s="2" t="s">
         <v>36</v>
       </c>
       <c r="F120" s="2">
-        <v>95</v>
+        <v>0</v>
       </c>
     </row>
     <row r="121" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A121" s="2" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="B121" s="2" t="s">
         <v>29</v>
@@ -2907,18 +2910,18 @@
         <v>22</v>
       </c>
       <c r="D121" s="2" t="s">
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="E121" s="2" t="s">
         <v>36</v>
       </c>
       <c r="F121" s="2">
-        <v>323</v>
+        <v>95</v>
       </c>
     </row>
     <row r="122" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A122" s="2" t="s">
-        <v>91</v>
+        <v>17</v>
       </c>
       <c r="B122" s="2" t="s">
         <v>29</v>
@@ -2927,58 +2930,58 @@
         <v>22</v>
       </c>
       <c r="D122" s="2" t="s">
-        <v>55</v>
+        <v>13</v>
       </c>
       <c r="E122" s="2" t="s">
         <v>36</v>
       </c>
       <c r="F122" s="2">
-        <v>0</v>
+        <v>323</v>
       </c>
     </row>
     <row r="123" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A123" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="B123" s="2">
-        <v>2026</v>
+        <v>91</v>
+      </c>
+      <c r="B123" s="2" t="s">
+        <v>29</v>
       </c>
       <c r="C123" s="2" t="s">
         <v>22</v>
       </c>
       <c r="D123" s="2" t="s">
-        <v>25</v>
+        <v>55</v>
       </c>
       <c r="E123" s="2" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="F123" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="124" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A124" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="B124" s="2" t="s">
-        <v>31</v>
+        <v>20</v>
+      </c>
+      <c r="B124" s="2">
+        <v>2026</v>
       </c>
       <c r="C124" s="2" t="s">
         <v>22</v>
       </c>
       <c r="D124" s="2" t="s">
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="E124" s="2" t="s">
         <v>42</v>
       </c>
       <c r="F124" s="2">
-        <v>66.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="125" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A125" s="2" t="s">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="B125" s="2" t="s">
         <v>31</v>
@@ -2987,27 +2990,27 @@
         <v>22</v>
       </c>
       <c r="D125" s="2" t="s">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="E125" s="2" t="s">
         <v>42</v>
       </c>
       <c r="F125" s="2">
-        <v>1</v>
+        <v>66.5</v>
       </c>
     </row>
     <row r="126" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A126" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="B126" s="2">
-        <v>2026</v>
+        <v>8</v>
+      </c>
+      <c r="B126" s="2" t="s">
+        <v>31</v>
       </c>
       <c r="C126" s="2" t="s">
         <v>22</v>
       </c>
       <c r="D126" s="2" t="s">
-        <v>23</v>
+        <v>4</v>
       </c>
       <c r="E126" s="2" t="s">
         <v>42</v>
@@ -3018,19 +3021,22 @@
     </row>
     <row r="127" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A127" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="B127" s="2" t="s">
-        <v>30</v>
+        <v>90</v>
+      </c>
+      <c r="B127" s="2">
+        <v>2026</v>
       </c>
       <c r="C127" s="2" t="s">
         <v>22</v>
       </c>
       <c r="D127" s="2" t="s">
-        <v>86</v>
+        <v>23</v>
       </c>
       <c r="E127" s="2" t="s">
-        <v>50</v>
+        <v>42</v>
+      </c>
+      <c r="F127" s="2">
+        <v>1</v>
       </c>
     </row>
     <row r="128" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -3038,7 +3044,7 @@
         <v>7</v>
       </c>
       <c r="B128" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C128" s="2" t="s">
         <v>22</v>
@@ -3047,7 +3053,7 @@
         <v>86</v>
       </c>
       <c r="E128" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="129" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -3055,7 +3061,7 @@
         <v>7</v>
       </c>
       <c r="B129" s="2" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C129" s="2" t="s">
         <v>22</v>
@@ -3064,24 +3070,24 @@
         <v>86</v>
       </c>
       <c r="E129" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="130" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A130" s="2" t="s">
-        <v>32</v>
+        <v>7</v>
       </c>
       <c r="B130" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C130" s="2" t="s">
         <v>22</v>
       </c>
       <c r="D130" s="2" t="s">
-        <v>32</v>
+        <v>86</v>
       </c>
       <c r="E130" s="2" t="s">
-        <v>73</v>
+        <v>52</v>
       </c>
     </row>
     <row r="131" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -3098,7 +3104,7 @@
         <v>32</v>
       </c>
       <c r="E131" s="2" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="132" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -3115,55 +3121,55 @@
         <v>32</v>
       </c>
       <c r="E132" s="2" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="133" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A133" s="2" t="s">
-        <v>13</v>
+        <v>32</v>
       </c>
       <c r="B133" s="2" t="s">
-        <v>13</v>
+        <v>32</v>
       </c>
       <c r="C133" s="2" t="s">
         <v>22</v>
       </c>
       <c r="D133" s="2" t="s">
-        <v>13</v>
+        <v>32</v>
       </c>
       <c r="E133" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="134" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A134" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B134" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C134" s="2" t="s">
         <v>22</v>
       </c>
       <c r="D134" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E134" s="2" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="135" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A135" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B135" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C135" s="2" t="s">
         <v>22</v>
       </c>
       <c r="D135" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E135" s="2" t="s">
         <v>77</v>
@@ -3171,53 +3177,53 @@
     </row>
     <row r="136" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A136" s="2" t="s">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="B136" s="2" t="s">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="C136" s="2" t="s">
         <v>22</v>
       </c>
       <c r="D136" s="2" t="s">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="E136" s="2" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="137" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A137" s="2" t="s">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="B137" s="2" t="s">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="C137" s="2" t="s">
         <v>22</v>
       </c>
       <c r="D137" s="2" t="s">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="E137" s="2" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="138" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A138" s="2" t="s">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="B138" s="2" t="s">
-        <v>30</v>
+        <v>13</v>
       </c>
       <c r="C138" s="2" t="s">
         <v>22</v>
       </c>
       <c r="D138" s="2" t="s">
-        <v>32</v>
+        <v>13</v>
       </c>
       <c r="E138" s="2" t="s">
-        <v>43</v>
+        <v>79</v>
       </c>
     </row>
     <row r="139" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -3225,7 +3231,7 @@
         <v>3</v>
       </c>
       <c r="B139" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C139" s="2" t="s">
         <v>22</v>
@@ -3234,7 +3240,7 @@
         <v>32</v>
       </c>
       <c r="E139" s="2" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
     </row>
     <row r="140" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -3242,7 +3248,7 @@
         <v>3</v>
       </c>
       <c r="B140" s="2" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C140" s="2" t="s">
         <v>22</v>
@@ -3251,38 +3257,38 @@
         <v>32</v>
       </c>
       <c r="E140" s="2" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
     </row>
     <row r="141" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A141" s="2" t="s">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="B141" s="2" t="s">
-        <v>12</v>
+        <v>31</v>
       </c>
       <c r="C141" s="2" t="s">
         <v>22</v>
       </c>
       <c r="D141" s="2" t="s">
-        <v>12</v>
+        <v>32</v>
       </c>
       <c r="E141" s="2" t="s">
-        <v>80</v>
+        <v>44</v>
       </c>
     </row>
     <row r="142" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A142" s="2" t="s">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="B142" s="2" t="s">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="C142" s="2" t="s">
         <v>22</v>
       </c>
       <c r="D142" s="2" t="s">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="E142" s="2" t="s">
         <v>80</v>
@@ -3290,16 +3296,16 @@
     </row>
     <row r="143" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A143" s="2" t="s">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="B143" s="2" t="s">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="C143" s="2" t="s">
         <v>22</v>
       </c>
       <c r="D143" s="2" t="s">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="E143" s="2" t="s">
         <v>80</v>
@@ -3307,16 +3313,16 @@
     </row>
     <row r="144" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A144" s="2" t="s">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="B144" s="2" t="s">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="C144" s="2" t="s">
         <v>22</v>
       </c>
       <c r="D144" s="2" t="s">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="E144" s="2" t="s">
         <v>80</v>
@@ -3324,16 +3330,16 @@
     </row>
     <row r="145" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A145" s="2" t="s">
-        <v>55</v>
+        <v>4</v>
       </c>
       <c r="B145" s="2" t="s">
-        <v>55</v>
+        <v>4</v>
       </c>
       <c r="C145" s="2" t="s">
         <v>22</v>
       </c>
       <c r="D145" s="2" t="s">
-        <v>55</v>
+        <v>4</v>
       </c>
       <c r="E145" s="2" t="s">
         <v>80</v>
@@ -3341,33 +3347,33 @@
     </row>
     <row r="146" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A146" s="2" t="s">
-        <v>12</v>
+        <v>55</v>
       </c>
       <c r="B146" s="2" t="s">
-        <v>12</v>
+        <v>55</v>
       </c>
       <c r="C146" s="2" t="s">
         <v>22</v>
       </c>
       <c r="D146" s="2" t="s">
-        <v>12</v>
+        <v>55</v>
       </c>
       <c r="E146" s="2" t="s">
-        <v>45</v>
+        <v>80</v>
       </c>
     </row>
     <row r="147" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A147" s="2" t="s">
-        <v>66</v>
+        <v>12</v>
       </c>
       <c r="B147" s="2" t="s">
-        <v>66</v>
+        <v>12</v>
       </c>
       <c r="C147" s="2" t="s">
         <v>22</v>
       </c>
       <c r="D147" s="2" t="s">
-        <v>66</v>
+        <v>12</v>
       </c>
       <c r="E147" s="2" t="s">
         <v>45</v>
@@ -3375,16 +3381,16 @@
     </row>
     <row r="148" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A148" s="2" t="s">
-        <v>24</v>
+        <v>66</v>
       </c>
       <c r="B148" s="2" t="s">
-        <v>24</v>
+        <v>66</v>
       </c>
       <c r="C148" s="2" t="s">
         <v>22</v>
       </c>
       <c r="D148" s="2" t="s">
-        <v>24</v>
+        <v>66</v>
       </c>
       <c r="E148" s="2" t="s">
         <v>45</v>
@@ -3392,16 +3398,16 @@
     </row>
     <row r="149" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A149" s="2" t="s">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="B149" s="2" t="s">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="C149" s="2" t="s">
         <v>22</v>
       </c>
       <c r="D149" s="2" t="s">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="E149" s="2" t="s">
         <v>45</v>
@@ -3409,16 +3415,16 @@
     </row>
     <row r="150" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A150" s="2" t="s">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="B150" s="2" t="s">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="C150" s="2" t="s">
         <v>22</v>
       </c>
       <c r="D150" s="2" t="s">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="E150" s="2" t="s">
         <v>45</v>
@@ -3426,16 +3432,16 @@
     </row>
     <row r="151" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A151" s="2" t="s">
-        <v>19</v>
+        <v>4</v>
       </c>
       <c r="B151" s="2" t="s">
-        <v>30</v>
+        <v>4</v>
       </c>
       <c r="C151" s="2" t="s">
         <v>22</v>
       </c>
       <c r="D151" s="2" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E151" s="2" t="s">
         <v>45</v>
@@ -3446,7 +3452,7 @@
         <v>19</v>
       </c>
       <c r="B152" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C152" s="2" t="s">
         <v>22</v>
@@ -3455,17 +3461,34 @@
         <v>5</v>
       </c>
       <c r="E152" s="2" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="153" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A153" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B153" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="C153" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="D153" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="E153" s="2" t="s">
         <v>38</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F152" xr:uid="{35372E75-D8AE-4D2B-8467-46A14CD55223}">
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:F152">
-      <sortCondition ref="E2:E152"/>
+  <autoFilter ref="A1:F153" xr:uid="{35372E75-D8AE-4D2B-8467-46A14CD55223}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:F153">
+      <sortCondition ref="E2:E153"/>
     </sortState>
   </autoFilter>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:F152">
-    <sortCondition ref="E2:E152"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:F153">
+    <sortCondition ref="E2:E153"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Siembra Ciclos Grupo ZP.xlsx
+++ b/Siembra Ciclos Grupo ZP.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ignag\Desktop\HTML PARA DB DA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{04770195-B142-4D8F-BEEA-BED78C7EC29D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3D6862B4-1502-4A56-BD66-0B9ADD8B2397}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -687,7 +687,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{35372E75-D8AE-4D2B-8467-46A14CD55223}">
-  <sheetPr codeName="Hoja1"/>
+  <sheetPr codeName="Hoja1" filterMode="1"/>
   <dimension ref="A1:F153"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
@@ -722,7 +722,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="2" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:6" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
         <v>57</v>
       </c>
@@ -739,7 +739,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="3" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:6" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
         <v>13</v>
       </c>
@@ -756,7 +756,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="4" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:6" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
         <v>57</v>
       </c>
@@ -773,7 +773,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="5" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:6" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
         <v>12</v>
       </c>
@@ -790,7 +790,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="6" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:6" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
         <v>13</v>
       </c>
@@ -807,7 +807,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="7" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:6" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
         <v>1</v>
       </c>
@@ -824,7 +824,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="8" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:6" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
         <v>57</v>
       </c>
@@ -841,7 +841,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="9" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:6" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
         <v>1</v>
       </c>
@@ -858,7 +858,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="10" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:6" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
         <v>1</v>
       </c>
@@ -875,7 +875,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="11" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:6" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="2" t="s">
         <v>57</v>
       </c>
@@ -892,7 +892,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="12" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:6" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="2" t="s">
         <v>12</v>
       </c>
@@ -909,7 +909,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="13" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:6" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="2" t="s">
         <v>24</v>
       </c>
@@ -926,7 +926,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="14" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:6" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="2" t="s">
         <v>13</v>
       </c>
@@ -943,7 +943,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="15" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:6" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="2" t="s">
         <v>4</v>
       </c>
@@ -960,7 +960,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="16" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:6" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="2" t="s">
         <v>57</v>
       </c>
@@ -977,7 +977,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="17" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:5" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="2" t="s">
         <v>12</v>
       </c>
@@ -994,7 +994,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="18" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:5" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="2" t="s">
         <v>24</v>
       </c>
@@ -1011,7 +1011,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="19" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:5" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="2" t="s">
         <v>13</v>
       </c>
@@ -1028,7 +1028,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="20" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:5" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="2" t="s">
         <v>4</v>
       </c>
@@ -1045,7 +1045,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="21" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:5" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="2" t="s">
         <v>57</v>
       </c>
@@ -1062,7 +1062,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="22" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:5" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="2" t="s">
         <v>6</v>
       </c>
@@ -1079,7 +1079,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="23" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:5" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="2" t="s">
         <v>12</v>
       </c>
@@ -1096,7 +1096,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="24" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:5" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="2" t="s">
         <v>24</v>
       </c>
@@ -1113,7 +1113,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="25" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:5" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="2" t="s">
         <v>13</v>
       </c>
@@ -1130,7 +1130,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="26" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:5" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="2" t="s">
         <v>4</v>
       </c>
@@ -1147,7 +1147,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="27" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:5" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="2" t="s">
         <v>6</v>
       </c>
@@ -1164,7 +1164,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="28" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:5" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="2" t="s">
         <v>6</v>
       </c>
@@ -1181,7 +1181,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="29" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:5" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="2" t="s">
         <v>12</v>
       </c>
@@ -1198,7 +1198,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="30" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:5" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="2" t="s">
         <v>13</v>
       </c>
@@ -1215,7 +1215,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="31" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:5" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="2" t="s">
         <v>9</v>
       </c>
@@ -1232,7 +1232,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="32" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:5" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="2" t="s">
         <v>10</v>
       </c>
@@ -1249,7 +1249,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="33" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:5" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="2" t="s">
         <v>9</v>
       </c>
@@ -1266,7 +1266,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="34" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:5" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" s="2" t="s">
         <v>10</v>
       </c>
@@ -1283,7 +1283,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="35" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:5" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" s="2" t="s">
         <v>9</v>
       </c>
@@ -1300,7 +1300,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="36" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:5" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A36" s="2" t="s">
         <v>12</v>
       </c>
@@ -1317,7 +1317,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="37" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:5" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A37" s="2" t="s">
         <v>23</v>
       </c>
@@ -1334,7 +1334,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="38" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:5" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" s="2" t="s">
         <v>24</v>
       </c>
@@ -1351,7 +1351,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="39" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:5" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A39" s="2" t="s">
         <v>13</v>
       </c>
@@ -1368,7 +1368,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="40" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:5" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A40" s="2" t="s">
         <v>57</v>
       </c>
@@ -1385,7 +1385,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="41" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:5" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A41" s="2" t="s">
         <v>12</v>
       </c>
@@ -1402,7 +1402,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="42" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:5" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A42" s="2" t="s">
         <v>23</v>
       </c>
@@ -1419,7 +1419,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="43" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:5" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A43" s="2" t="s">
         <v>24</v>
       </c>
@@ -1436,7 +1436,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="44" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:5" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A44" s="2" t="s">
         <v>13</v>
       </c>
@@ -1453,7 +1453,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="45" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:5" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A45" s="2" t="s">
         <v>12</v>
       </c>
@@ -1470,7 +1470,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="46" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:5" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A46" s="2" t="s">
         <v>23</v>
       </c>
@@ -1487,7 +1487,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="47" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:5" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A47" s="2" t="s">
         <v>24</v>
       </c>
@@ -1504,7 +1504,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="48" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:5" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A48" s="2" t="s">
         <v>4</v>
       </c>
@@ -1521,7 +1521,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="49" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:6" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A49" s="2" t="s">
         <v>12</v>
       </c>
@@ -1538,7 +1538,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="50" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:6" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A50" s="2" t="s">
         <v>23</v>
       </c>
@@ -1558,7 +1558,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="51" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:6" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A51" s="2" t="s">
         <v>24</v>
       </c>
@@ -1578,7 +1578,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="52" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:6" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A52" s="2" t="s">
         <v>13</v>
       </c>
@@ -1595,7 +1595,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="53" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:6" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A53" s="2" t="s">
         <v>4</v>
       </c>
@@ -1615,7 +1615,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="54" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:6" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A54" s="2" t="s">
         <v>12</v>
       </c>
@@ -1635,7 +1635,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="55" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:6" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A55" s="2" t="s">
         <v>66</v>
       </c>
@@ -1652,7 +1652,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="56" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:6" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A56" s="2" t="s">
         <v>23</v>
       </c>
@@ -1672,7 +1672,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="57" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:6" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A57" s="2" t="s">
         <v>24</v>
       </c>
@@ -1692,7 +1692,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="58" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:6" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A58" s="2" t="s">
         <v>4</v>
       </c>
@@ -1712,7 +1712,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="59" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:6" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A59" s="2" t="s">
         <v>12</v>
       </c>
@@ -1732,7 +1732,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="60" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:6" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A60" s="2" t="s">
         <v>66</v>
       </c>
@@ -1749,7 +1749,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="61" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:6" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A61" s="2" t="s">
         <v>23</v>
       </c>
@@ -1766,7 +1766,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="62" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:6" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A62" s="2" t="s">
         <v>24</v>
       </c>
@@ -1786,7 +1786,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="63" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:6" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A63" s="2" t="s">
         <v>4</v>
       </c>
@@ -1806,7 +1806,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="64" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:6" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A64" s="2" t="s">
         <v>16</v>
       </c>
@@ -1826,7 +1826,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="65" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:6" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A65" s="2" t="s">
         <v>18</v>
       </c>
@@ -1846,7 +1846,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="66" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:6" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A66" s="2" t="s">
         <v>2</v>
       </c>
@@ -1866,7 +1866,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="67" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:6" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A67" s="2" t="s">
         <v>14</v>
       </c>
@@ -1886,7 +1886,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="68" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:6" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A68" s="2" t="s">
         <v>16</v>
       </c>
@@ -1907,7 +1907,7 @@
         <v>75.259999999999991</v>
       </c>
     </row>
-    <row r="69" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:6" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A69" s="2" t="s">
         <v>2</v>
       </c>
@@ -1928,7 +1928,7 @@
         <v>201.64</v>
       </c>
     </row>
-    <row r="70" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:6" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A70" s="2" t="s">
         <v>15</v>
       </c>
@@ -1949,7 +1949,7 @@
         <v>75.259999999999991</v>
       </c>
     </row>
-    <row r="71" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:6" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A71" s="2" t="s">
         <v>14</v>
       </c>
@@ -1970,7 +1970,7 @@
         <v>96.56</v>
       </c>
     </row>
-    <row r="72" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:6" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A72" s="2" t="s">
         <v>12</v>
       </c>
@@ -1987,7 +1987,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="73" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:6" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A73" s="2" t="s">
         <v>11</v>
       </c>
@@ -2004,7 +2004,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="74" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:6" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A74" s="2" t="s">
         <v>13</v>
       </c>
@@ -2021,7 +2021,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="75" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:6" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A75" s="2" t="s">
         <v>4</v>
       </c>
@@ -2038,7 +2038,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="76" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:6" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A76" s="2" t="s">
         <v>13</v>
       </c>
@@ -2055,7 +2055,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="77" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:6" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A77" s="2" t="s">
         <v>12</v>
       </c>
@@ -2072,7 +2072,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="78" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:6" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A78" s="2" t="s">
         <v>70</v>
       </c>
@@ -2092,7 +2092,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="79" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:6" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A79" s="2" t="s">
         <v>24</v>
       </c>
@@ -2109,7 +2109,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="80" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:6" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A80" s="2" t="s">
         <v>13</v>
       </c>
@@ -2129,7 +2129,7 @@
         <v>425</v>
       </c>
     </row>
-    <row r="81" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:6" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A81" s="2" t="s">
         <v>4</v>
       </c>
@@ -2149,7 +2149,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="82" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:6" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A82" s="2" t="s">
         <v>55</v>
       </c>
@@ -2169,7 +2169,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="83" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:6" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A83" s="2" t="s">
         <v>32</v>
       </c>
@@ -2186,7 +2186,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="84" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:6" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A84" s="2" t="s">
         <v>57</v>
       </c>
@@ -2203,7 +2203,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="85" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:6" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A85" s="2" t="s">
         <v>12</v>
       </c>
@@ -2223,7 +2223,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="86" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:6" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A86" s="2" t="s">
         <v>70</v>
       </c>
@@ -2243,7 +2243,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="87" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:6" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A87" s="2" t="s">
         <v>13</v>
       </c>
@@ -2263,7 +2263,7 @@
         <v>441.5</v>
       </c>
     </row>
-    <row r="88" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:6" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A88" s="2" t="s">
         <v>4</v>
       </c>
@@ -2283,7 +2283,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="89" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:6" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A89" s="2" t="s">
         <v>55</v>
       </c>
@@ -2303,7 +2303,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="90" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:6" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A90" s="2" t="s">
         <v>32</v>
       </c>
@@ -2320,7 +2320,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="91" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:6" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A91" s="2" t="s">
         <v>57</v>
       </c>
@@ -2337,7 +2337,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="92" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:6" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A92" s="2" t="s">
         <v>12</v>
       </c>
@@ -2357,7 +2357,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="93" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:6" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A93" s="2" t="s">
         <v>23</v>
       </c>
@@ -2374,7 +2374,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="94" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:6" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A94" s="2" t="s">
         <v>24</v>
       </c>
@@ -2391,7 +2391,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="95" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:6" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A95" s="2" t="s">
         <v>13</v>
       </c>
@@ -2411,7 +2411,7 @@
         <v>466.5</v>
       </c>
     </row>
-    <row r="96" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:6" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A96" s="2" t="s">
         <v>4</v>
       </c>
@@ -2431,7 +2431,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="97" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:6" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A97" s="2" t="s">
         <v>55</v>
       </c>
@@ -2451,7 +2451,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="98" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:6" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A98" s="2" t="s">
         <v>32</v>
       </c>
@@ -2468,7 +2468,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="99" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:6" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A99" s="2" t="s">
         <v>12</v>
       </c>
@@ -2488,7 +2488,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="100" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:6" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A100" s="2" t="s">
         <v>13</v>
       </c>
@@ -2508,7 +2508,7 @@
         <v>463</v>
       </c>
     </row>
-    <row r="101" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:6" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A101" s="2" t="s">
         <v>4</v>
       </c>
@@ -2528,7 +2528,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="102" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:6" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A102" s="2" t="s">
         <v>55</v>
       </c>
@@ -2548,7 +2548,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="103" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:6" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A103" s="2" t="s">
         <v>32</v>
       </c>
@@ -2565,7 +2565,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="104" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:6" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A104" s="2" t="s">
         <v>12</v>
       </c>
@@ -2585,7 +2585,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="105" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:6" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A105" s="2" t="s">
         <v>13</v>
       </c>
@@ -2605,7 +2605,7 @@
         <v>473</v>
       </c>
     </row>
-    <row r="106" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:6" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A106" s="2" t="s">
         <v>4</v>
       </c>
@@ -2625,7 +2625,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="107" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:6" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A107" s="2" t="s">
         <v>55</v>
       </c>
@@ -2645,7 +2645,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="108" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:6" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A108" s="2" t="s">
         <v>32</v>
       </c>
@@ -2662,7 +2662,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="109" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:6" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A109" s="2" t="s">
         <v>12</v>
       </c>
@@ -2682,7 +2682,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="110" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:6" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A110" s="2" t="s">
         <v>89</v>
       </c>
@@ -2702,7 +2702,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="111" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:6" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A111" s="2" t="s">
         <v>90</v>
       </c>
@@ -2722,7 +2722,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="112" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:6" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A112" s="2" t="s">
         <v>17</v>
       </c>
@@ -2742,7 +2742,7 @@
         <v>483</v>
       </c>
     </row>
-    <row r="113" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:6" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A113" s="2" t="s">
         <v>13</v>
       </c>
@@ -2762,7 +2762,7 @@
         <v>483</v>
       </c>
     </row>
-    <row r="114" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:6" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A114" s="2" t="s">
         <v>92</v>
       </c>
@@ -2782,7 +2782,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="115" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:6" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A115" s="2" t="s">
         <v>4</v>
       </c>
@@ -2802,7 +2802,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="116" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:6" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A116" s="2" t="s">
         <v>91</v>
       </c>
@@ -2822,7 +2822,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="117" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:6" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A117" s="2" t="s">
         <v>55</v>
       </c>
@@ -2842,7 +2842,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="118" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:6" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A118" s="2" t="s">
         <v>32</v>
       </c>
@@ -2859,7 +2859,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="119" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:6" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A119" s="2" t="s">
         <v>89</v>
       </c>
@@ -2879,7 +2879,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="120" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:6" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A120" s="2" t="s">
         <v>90</v>
       </c>
@@ -2899,7 +2899,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="121" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:6" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A121" s="2" t="s">
         <v>20</v>
       </c>
@@ -2919,7 +2919,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="122" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:6" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A122" s="2" t="s">
         <v>17</v>
       </c>
@@ -2939,7 +2939,7 @@
         <v>323</v>
       </c>
     </row>
-    <row r="123" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:6" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A123" s="2" t="s">
         <v>91</v>
       </c>
@@ -2976,7 +2976,7 @@
         <v>42</v>
       </c>
       <c r="F124" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="125" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -2996,7 +2996,8 @@
         <v>42</v>
       </c>
       <c r="F125" s="2">
-        <v>66.5</v>
+        <f>66.5+29.5</f>
+        <v>96</v>
       </c>
     </row>
     <row r="126" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -3016,7 +3017,7 @@
         <v>42</v>
       </c>
       <c r="F126" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="127" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -3036,10 +3037,10 @@
         <v>42</v>
       </c>
       <c r="F127" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="128" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="128" spans="1:6" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A128" s="2" t="s">
         <v>7</v>
       </c>
@@ -3056,7 +3057,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="129" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:5" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A129" s="2" t="s">
         <v>7</v>
       </c>
@@ -3073,7 +3074,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="130" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:5" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A130" s="2" t="s">
         <v>7</v>
       </c>
@@ -3090,7 +3091,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="131" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:5" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A131" s="2" t="s">
         <v>32</v>
       </c>
@@ -3107,7 +3108,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="132" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:5" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A132" s="2" t="s">
         <v>32</v>
       </c>
@@ -3124,7 +3125,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="133" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:5" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A133" s="2" t="s">
         <v>32</v>
       </c>
@@ -3141,7 +3142,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="134" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:5" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A134" s="2" t="s">
         <v>13</v>
       </c>
@@ -3158,7 +3159,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="135" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:5" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A135" s="2" t="s">
         <v>12</v>
       </c>
@@ -3175,7 +3176,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="136" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:5" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A136" s="2" t="s">
         <v>13</v>
       </c>
@@ -3192,7 +3193,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="137" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:5" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A137" s="2" t="s">
         <v>23</v>
       </c>
@@ -3209,7 +3210,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="138" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:5" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A138" s="2" t="s">
         <v>13</v>
       </c>
@@ -3226,7 +3227,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="139" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:5" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A139" s="2" t="s">
         <v>3</v>
       </c>
@@ -3243,7 +3244,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="140" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:5" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A140" s="2" t="s">
         <v>3</v>
       </c>
@@ -3260,7 +3261,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="141" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:5" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A141" s="2" t="s">
         <v>3</v>
       </c>
@@ -3277,7 +3278,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="142" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:5" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A142" s="2" t="s">
         <v>12</v>
       </c>
@@ -3294,7 +3295,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="143" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:5" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A143" s="2" t="s">
         <v>23</v>
       </c>
@@ -3311,7 +3312,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="144" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:5" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A144" s="2" t="s">
         <v>13</v>
       </c>
@@ -3328,7 +3329,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="145" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:5" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A145" s="2" t="s">
         <v>4</v>
       </c>
@@ -3345,7 +3346,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="146" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:5" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A146" s="2" t="s">
         <v>55</v>
       </c>
@@ -3362,7 +3363,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="147" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:5" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A147" s="2" t="s">
         <v>12</v>
       </c>
@@ -3379,7 +3380,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="148" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:5" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A148" s="2" t="s">
         <v>66</v>
       </c>
@@ -3396,7 +3397,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="149" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:5" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A149" s="2" t="s">
         <v>24</v>
       </c>
@@ -3413,7 +3414,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="150" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:5" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A150" s="2" t="s">
         <v>13</v>
       </c>
@@ -3430,7 +3431,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="151" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:5" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A151" s="2" t="s">
         <v>4</v>
       </c>
@@ -3447,7 +3448,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="152" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:5" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A152" s="2" t="s">
         <v>19</v>
       </c>
@@ -3464,7 +3465,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="153" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:5" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A153" s="2" t="s">
         <v>19</v>
       </c>
@@ -3483,6 +3484,11 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:F153" xr:uid="{35372E75-D8AE-4D2B-8467-46A14CD55223}">
+    <filterColumn colId="4">
+      <filters>
+        <filter val="Mani 2026"/>
+      </filters>
+    </filterColumn>
     <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:F153">
       <sortCondition ref="E2:E153"/>
     </sortState>

--- a/Siembra Ciclos Grupo ZP.xlsx
+++ b/Siembra Ciclos Grupo ZP.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ignag\Desktop\HTML PARA DB DA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3D6862B4-1502-4A56-BD66-0B9ADD8B2397}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F9A738A2-1C38-491F-AC65-F30F34A056F7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="762" uniqueCount="93">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="764" uniqueCount="93">
   <si>
     <t>Cuenta Analitica en Recibo de Pago</t>
   </si>
@@ -687,7 +687,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{35372E75-D8AE-4D2B-8467-46A14CD55223}">
-  <sheetPr codeName="Hoja1" filterMode="1"/>
+  <sheetPr codeName="Hoja1"/>
   <dimension ref="A1:F153"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
@@ -722,7 +722,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="2" spans="1:6" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
         <v>57</v>
       </c>
@@ -739,7 +739,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="3" spans="1:6" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
         <v>13</v>
       </c>
@@ -756,7 +756,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="4" spans="1:6" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
         <v>57</v>
       </c>
@@ -773,7 +773,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="5" spans="1:6" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
         <v>12</v>
       </c>
@@ -790,7 +790,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="6" spans="1:6" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
         <v>13</v>
       </c>
@@ -807,7 +807,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="7" spans="1:6" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
         <v>1</v>
       </c>
@@ -824,7 +824,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="8" spans="1:6" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
         <v>57</v>
       </c>
@@ -841,7 +841,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="9" spans="1:6" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
         <v>1</v>
       </c>
@@ -858,7 +858,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="10" spans="1:6" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
         <v>1</v>
       </c>
@@ -875,7 +875,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="11" spans="1:6" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="2" t="s">
         <v>57</v>
       </c>
@@ -892,7 +892,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="12" spans="1:6" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="2" t="s">
         <v>12</v>
       </c>
@@ -909,7 +909,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="13" spans="1:6" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="2" t="s">
         <v>24</v>
       </c>
@@ -926,7 +926,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="14" spans="1:6" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="2" t="s">
         <v>13</v>
       </c>
@@ -943,7 +943,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="15" spans="1:6" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="2" t="s">
         <v>4</v>
       </c>
@@ -960,7 +960,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="16" spans="1:6" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="2" t="s">
         <v>57</v>
       </c>
@@ -977,7 +977,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="17" spans="1:5" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="2" t="s">
         <v>12</v>
       </c>
@@ -994,7 +994,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="18" spans="1:5" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="2" t="s">
         <v>24</v>
       </c>
@@ -1011,7 +1011,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="19" spans="1:5" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="2" t="s">
         <v>13</v>
       </c>
@@ -1028,7 +1028,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="20" spans="1:5" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="2" t="s">
         <v>4</v>
       </c>
@@ -1045,7 +1045,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="21" spans="1:5" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="2" t="s">
         <v>57</v>
       </c>
@@ -1062,7 +1062,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="22" spans="1:5" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="2" t="s">
         <v>6</v>
       </c>
@@ -1079,7 +1079,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="23" spans="1:5" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="2" t="s">
         <v>12</v>
       </c>
@@ -1096,7 +1096,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="24" spans="1:5" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="2" t="s">
         <v>24</v>
       </c>
@@ -1113,7 +1113,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="25" spans="1:5" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="2" t="s">
         <v>13</v>
       </c>
@@ -1130,7 +1130,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="26" spans="1:5" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="2" t="s">
         <v>4</v>
       </c>
@@ -1147,7 +1147,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="27" spans="1:5" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="2" t="s">
         <v>6</v>
       </c>
@@ -1164,7 +1164,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="28" spans="1:5" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="2" t="s">
         <v>6</v>
       </c>
@@ -1181,7 +1181,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="29" spans="1:5" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="2" t="s">
         <v>12</v>
       </c>
@@ -1198,7 +1198,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="30" spans="1:5" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="2" t="s">
         <v>13</v>
       </c>
@@ -1215,7 +1215,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="31" spans="1:5" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="2" t="s">
         <v>9</v>
       </c>
@@ -1232,7 +1232,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="32" spans="1:5" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="2" t="s">
         <v>10</v>
       </c>
@@ -1249,7 +1249,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="33" spans="1:5" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="2" t="s">
         <v>9</v>
       </c>
@@ -1266,7 +1266,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="34" spans="1:5" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" s="2" t="s">
         <v>10</v>
       </c>
@@ -1283,7 +1283,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="35" spans="1:5" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" s="2" t="s">
         <v>9</v>
       </c>
@@ -1300,7 +1300,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="36" spans="1:5" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A36" s="2" t="s">
         <v>12</v>
       </c>
@@ -1317,7 +1317,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="37" spans="1:5" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A37" s="2" t="s">
         <v>23</v>
       </c>
@@ -1334,7 +1334,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="38" spans="1:5" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" s="2" t="s">
         <v>24</v>
       </c>
@@ -1351,7 +1351,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="39" spans="1:5" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A39" s="2" t="s">
         <v>13</v>
       </c>
@@ -1368,7 +1368,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="40" spans="1:5" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A40" s="2" t="s">
         <v>57</v>
       </c>
@@ -1385,7 +1385,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="41" spans="1:5" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A41" s="2" t="s">
         <v>12</v>
       </c>
@@ -1402,7 +1402,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="42" spans="1:5" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A42" s="2" t="s">
         <v>23</v>
       </c>
@@ -1419,7 +1419,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="43" spans="1:5" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A43" s="2" t="s">
         <v>24</v>
       </c>
@@ -1436,7 +1436,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="44" spans="1:5" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A44" s="2" t="s">
         <v>13</v>
       </c>
@@ -1453,7 +1453,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="45" spans="1:5" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A45" s="2" t="s">
         <v>12</v>
       </c>
@@ -1470,7 +1470,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="46" spans="1:5" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A46" s="2" t="s">
         <v>23</v>
       </c>
@@ -1487,7 +1487,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="47" spans="1:5" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A47" s="2" t="s">
         <v>24</v>
       </c>
@@ -1504,7 +1504,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="48" spans="1:5" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A48" s="2" t="s">
         <v>4</v>
       </c>
@@ -1521,7 +1521,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="49" spans="1:6" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A49" s="2" t="s">
         <v>12</v>
       </c>
@@ -1538,7 +1538,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="50" spans="1:6" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A50" s="2" t="s">
         <v>23</v>
       </c>
@@ -1558,7 +1558,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="51" spans="1:6" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A51" s="2" t="s">
         <v>24</v>
       </c>
@@ -1578,7 +1578,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="52" spans="1:6" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A52" s="2" t="s">
         <v>13</v>
       </c>
@@ -1595,7 +1595,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="53" spans="1:6" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A53" s="2" t="s">
         <v>4</v>
       </c>
@@ -1615,7 +1615,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="54" spans="1:6" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A54" s="2" t="s">
         <v>12</v>
       </c>
@@ -1635,7 +1635,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="55" spans="1:6" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A55" s="2" t="s">
         <v>66</v>
       </c>
@@ -1652,7 +1652,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="56" spans="1:6" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A56" s="2" t="s">
         <v>23</v>
       </c>
@@ -1672,7 +1672,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="57" spans="1:6" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A57" s="2" t="s">
         <v>24</v>
       </c>
@@ -1692,7 +1692,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="58" spans="1:6" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A58" s="2" t="s">
         <v>4</v>
       </c>
@@ -1712,7 +1712,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="59" spans="1:6" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A59" s="2" t="s">
         <v>12</v>
       </c>
@@ -1732,7 +1732,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="60" spans="1:6" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A60" s="2" t="s">
         <v>66</v>
       </c>
@@ -1749,7 +1749,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="61" spans="1:6" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A61" s="2" t="s">
         <v>23</v>
       </c>
@@ -1766,7 +1766,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="62" spans="1:6" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A62" s="2" t="s">
         <v>24</v>
       </c>
@@ -1786,7 +1786,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="63" spans="1:6" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A63" s="2" t="s">
         <v>4</v>
       </c>
@@ -1806,7 +1806,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="64" spans="1:6" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A64" s="2" t="s">
         <v>16</v>
       </c>
@@ -1826,7 +1826,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="65" spans="1:6" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A65" s="2" t="s">
         <v>18</v>
       </c>
@@ -1846,7 +1846,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="66" spans="1:6" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A66" s="2" t="s">
         <v>2</v>
       </c>
@@ -1866,7 +1866,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="67" spans="1:6" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A67" s="2" t="s">
         <v>14</v>
       </c>
@@ -1886,7 +1886,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="68" spans="1:6" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A68" s="2" t="s">
         <v>16</v>
       </c>
@@ -1907,7 +1907,7 @@
         <v>75.259999999999991</v>
       </c>
     </row>
-    <row r="69" spans="1:6" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A69" s="2" t="s">
         <v>2</v>
       </c>
@@ -1928,7 +1928,7 @@
         <v>201.64</v>
       </c>
     </row>
-    <row r="70" spans="1:6" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A70" s="2" t="s">
         <v>15</v>
       </c>
@@ -1949,7 +1949,7 @@
         <v>75.259999999999991</v>
       </c>
     </row>
-    <row r="71" spans="1:6" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A71" s="2" t="s">
         <v>14</v>
       </c>
@@ -1970,7 +1970,7 @@
         <v>96.56</v>
       </c>
     </row>
-    <row r="72" spans="1:6" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A72" s="2" t="s">
         <v>12</v>
       </c>
@@ -1987,7 +1987,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="73" spans="1:6" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A73" s="2" t="s">
         <v>11</v>
       </c>
@@ -2004,7 +2004,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="74" spans="1:6" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A74" s="2" t="s">
         <v>13</v>
       </c>
@@ -2021,7 +2021,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="75" spans="1:6" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A75" s="2" t="s">
         <v>4</v>
       </c>
@@ -2038,7 +2038,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="76" spans="1:6" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A76" s="2" t="s">
         <v>13</v>
       </c>
@@ -2055,7 +2055,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="77" spans="1:6" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A77" s="2" t="s">
         <v>12</v>
       </c>
@@ -2072,7 +2072,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="78" spans="1:6" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A78" s="2" t="s">
         <v>70</v>
       </c>
@@ -2092,7 +2092,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="79" spans="1:6" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A79" s="2" t="s">
         <v>24</v>
       </c>
@@ -2109,7 +2109,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="80" spans="1:6" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A80" s="2" t="s">
         <v>13</v>
       </c>
@@ -2129,7 +2129,7 @@
         <v>425</v>
       </c>
     </row>
-    <row r="81" spans="1:6" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A81" s="2" t="s">
         <v>4</v>
       </c>
@@ -2149,7 +2149,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="82" spans="1:6" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A82" s="2" t="s">
         <v>55</v>
       </c>
@@ -2169,7 +2169,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="83" spans="1:6" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A83" s="2" t="s">
         <v>32</v>
       </c>
@@ -2186,7 +2186,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="84" spans="1:6" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A84" s="2" t="s">
         <v>57</v>
       </c>
@@ -2203,7 +2203,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="85" spans="1:6" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A85" s="2" t="s">
         <v>12</v>
       </c>
@@ -2223,7 +2223,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="86" spans="1:6" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A86" s="2" t="s">
         <v>70</v>
       </c>
@@ -2243,7 +2243,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="87" spans="1:6" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A87" s="2" t="s">
         <v>13</v>
       </c>
@@ -2263,7 +2263,7 @@
         <v>441.5</v>
       </c>
     </row>
-    <row r="88" spans="1:6" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A88" s="2" t="s">
         <v>4</v>
       </c>
@@ -2283,7 +2283,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="89" spans="1:6" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A89" s="2" t="s">
         <v>55</v>
       </c>
@@ -2303,7 +2303,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="90" spans="1:6" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A90" s="2" t="s">
         <v>32</v>
       </c>
@@ -2320,7 +2320,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="91" spans="1:6" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A91" s="2" t="s">
         <v>57</v>
       </c>
@@ -2337,7 +2337,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="92" spans="1:6" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A92" s="2" t="s">
         <v>12</v>
       </c>
@@ -2357,7 +2357,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="93" spans="1:6" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A93" s="2" t="s">
         <v>23</v>
       </c>
@@ -2374,7 +2374,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="94" spans="1:6" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A94" s="2" t="s">
         <v>24</v>
       </c>
@@ -2391,7 +2391,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="95" spans="1:6" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A95" s="2" t="s">
         <v>13</v>
       </c>
@@ -2411,7 +2411,7 @@
         <v>466.5</v>
       </c>
     </row>
-    <row r="96" spans="1:6" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A96" s="2" t="s">
         <v>4</v>
       </c>
@@ -2431,7 +2431,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="97" spans="1:6" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A97" s="2" t="s">
         <v>55</v>
       </c>
@@ -2451,7 +2451,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="98" spans="1:6" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A98" s="2" t="s">
         <v>32</v>
       </c>
@@ -2468,7 +2468,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="99" spans="1:6" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A99" s="2" t="s">
         <v>12</v>
       </c>
@@ -2488,7 +2488,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="100" spans="1:6" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A100" s="2" t="s">
         <v>13</v>
       </c>
@@ -2508,7 +2508,7 @@
         <v>463</v>
       </c>
     </row>
-    <row r="101" spans="1:6" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A101" s="2" t="s">
         <v>4</v>
       </c>
@@ -2528,7 +2528,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="102" spans="1:6" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A102" s="2" t="s">
         <v>55</v>
       </c>
@@ -2548,7 +2548,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="103" spans="1:6" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A103" s="2" t="s">
         <v>32</v>
       </c>
@@ -2565,7 +2565,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="104" spans="1:6" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A104" s="2" t="s">
         <v>12</v>
       </c>
@@ -2585,7 +2585,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="105" spans="1:6" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A105" s="2" t="s">
         <v>13</v>
       </c>
@@ -2605,7 +2605,7 @@
         <v>473</v>
       </c>
     </row>
-    <row r="106" spans="1:6" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A106" s="2" t="s">
         <v>4</v>
       </c>
@@ -2625,7 +2625,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="107" spans="1:6" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A107" s="2" t="s">
         <v>55</v>
       </c>
@@ -2645,7 +2645,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="108" spans="1:6" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A108" s="2" t="s">
         <v>32</v>
       </c>
@@ -2662,7 +2662,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="109" spans="1:6" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A109" s="2" t="s">
         <v>12</v>
       </c>
@@ -2682,7 +2682,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="110" spans="1:6" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A110" s="2" t="s">
         <v>89</v>
       </c>
@@ -2699,10 +2699,10 @@
         <v>41</v>
       </c>
       <c r="F110" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="111" spans="1:6" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="111" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A111" s="2" t="s">
         <v>90</v>
       </c>
@@ -2722,7 +2722,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="112" spans="1:6" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A112" s="2" t="s">
         <v>17</v>
       </c>
@@ -2742,7 +2742,7 @@
         <v>483</v>
       </c>
     </row>
-    <row r="113" spans="1:6" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A113" s="2" t="s">
         <v>13</v>
       </c>
@@ -2762,12 +2762,12 @@
         <v>483</v>
       </c>
     </row>
-    <row r="114" spans="1:6" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A114" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="B114" s="2">
-        <v>2024</v>
+      <c r="B114" s="2" t="s">
+        <v>30</v>
       </c>
       <c r="C114" s="2" t="s">
         <v>22</v>
@@ -2782,7 +2782,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="115" spans="1:6" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A115" s="2" t="s">
         <v>4</v>
       </c>
@@ -2802,7 +2802,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="116" spans="1:6" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A116" s="2" t="s">
         <v>91</v>
       </c>
@@ -2822,7 +2822,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="117" spans="1:6" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A117" s="2" t="s">
         <v>55</v>
       </c>
@@ -2842,7 +2842,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="118" spans="1:6" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A118" s="2" t="s">
         <v>32</v>
       </c>
@@ -2859,7 +2859,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="119" spans="1:6" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A119" s="2" t="s">
         <v>89</v>
       </c>
@@ -2879,7 +2879,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="120" spans="1:6" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A120" s="2" t="s">
         <v>90</v>
       </c>
@@ -2899,7 +2899,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="121" spans="1:6" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A121" s="2" t="s">
         <v>20</v>
       </c>
@@ -2919,7 +2919,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="122" spans="1:6" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A122" s="2" t="s">
         <v>17</v>
       </c>
@@ -2939,7 +2939,7 @@
         <v>323</v>
       </c>
     </row>
-    <row r="123" spans="1:6" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A123" s="2" t="s">
         <v>91</v>
       </c>
@@ -3024,8 +3024,8 @@
       <c r="A127" s="2" t="s">
         <v>90</v>
       </c>
-      <c r="B127" s="2">
-        <v>2026</v>
+      <c r="B127" s="2" t="s">
+        <v>31</v>
       </c>
       <c r="C127" s="2" t="s">
         <v>22</v>
@@ -3040,7 +3040,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="128" spans="1:6" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A128" s="2" t="s">
         <v>7</v>
       </c>
@@ -3057,7 +3057,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="129" spans="1:5" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A129" s="2" t="s">
         <v>7</v>
       </c>
@@ -3074,7 +3074,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="130" spans="1:5" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A130" s="2" t="s">
         <v>7</v>
       </c>
@@ -3091,7 +3091,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="131" spans="1:5" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A131" s="2" t="s">
         <v>32</v>
       </c>
@@ -3108,7 +3108,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="132" spans="1:5" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A132" s="2" t="s">
         <v>32</v>
       </c>
@@ -3125,7 +3125,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="133" spans="1:5" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A133" s="2" t="s">
         <v>32</v>
       </c>
@@ -3142,7 +3142,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="134" spans="1:5" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A134" s="2" t="s">
         <v>13</v>
       </c>
@@ -3159,7 +3159,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="135" spans="1:5" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A135" s="2" t="s">
         <v>12</v>
       </c>
@@ -3176,7 +3176,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="136" spans="1:5" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A136" s="2" t="s">
         <v>13</v>
       </c>
@@ -3193,7 +3193,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="137" spans="1:5" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A137" s="2" t="s">
         <v>23</v>
       </c>
@@ -3210,7 +3210,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="138" spans="1:5" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A138" s="2" t="s">
         <v>13</v>
       </c>
@@ -3227,7 +3227,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="139" spans="1:5" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A139" s="2" t="s">
         <v>3</v>
       </c>
@@ -3244,7 +3244,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="140" spans="1:5" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A140" s="2" t="s">
         <v>3</v>
       </c>
@@ -3261,7 +3261,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="141" spans="1:5" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A141" s="2" t="s">
         <v>3</v>
       </c>
@@ -3278,7 +3278,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="142" spans="1:5" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A142" s="2" t="s">
         <v>12</v>
       </c>
@@ -3295,7 +3295,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="143" spans="1:5" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A143" s="2" t="s">
         <v>23</v>
       </c>
@@ -3312,7 +3312,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="144" spans="1:5" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A144" s="2" t="s">
         <v>13</v>
       </c>
@@ -3329,7 +3329,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="145" spans="1:5" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A145" s="2" t="s">
         <v>4</v>
       </c>
@@ -3346,7 +3346,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="146" spans="1:5" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A146" s="2" t="s">
         <v>55</v>
       </c>
@@ -3363,7 +3363,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="147" spans="1:5" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A147" s="2" t="s">
         <v>12</v>
       </c>
@@ -3380,7 +3380,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="148" spans="1:5" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A148" s="2" t="s">
         <v>66</v>
       </c>
@@ -3397,7 +3397,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="149" spans="1:5" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A149" s="2" t="s">
         <v>24</v>
       </c>
@@ -3414,7 +3414,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="150" spans="1:5" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A150" s="2" t="s">
         <v>13</v>
       </c>
@@ -3431,7 +3431,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="151" spans="1:5" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A151" s="2" t="s">
         <v>4</v>
       </c>
@@ -3448,7 +3448,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="152" spans="1:5" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A152" s="2" t="s">
         <v>19</v>
       </c>
@@ -3465,7 +3465,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="153" spans="1:5" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A153" s="2" t="s">
         <v>19</v>
       </c>
@@ -3484,11 +3484,6 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:F153" xr:uid="{35372E75-D8AE-4D2B-8467-46A14CD55223}">
-    <filterColumn colId="4">
-      <filters>
-        <filter val="Mani 2026"/>
-      </filters>
-    </filterColumn>
     <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:F153">
       <sortCondition ref="E2:E153"/>
     </sortState>

--- a/Siembra Ciclos Grupo ZP.xlsx
+++ b/Siembra Ciclos Grupo ZP.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ignag\Desktop\HTML PARA DB DA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{50295F81-BCCE-4EF6-9F56-120328E7F691}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{62D79205-9980-4326-81C6-916B938F74A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="38640" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Relacion analiticas vs fincas" sheetId="2" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Relacion analiticas vs fincas'!$A$1:$F$99</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Relacion analiticas vs fincas'!$A$1:$F$118</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="494" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="589" uniqueCount="62">
   <si>
     <t>Cuenta Analitica en Recibo de Pago</t>
   </si>
@@ -209,7 +209,19 @@
     <t>[MANI] Mani Rancho Pando</t>
   </si>
   <si>
-    <t>[MANI] Paraiso</t>
+    <t>2019</t>
+  </si>
+  <si>
+    <t>2020</t>
+  </si>
+  <si>
+    <t>2021</t>
+  </si>
+  <si>
+    <t>2022</t>
+  </si>
+  <si>
+    <t>2023</t>
   </si>
 </sst>
 </file>
@@ -583,7 +595,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{35372E75-D8AE-4D2B-8467-46A14CD55223}">
   <sheetPr codeName="Hoja1"/>
-  <dimension ref="A1:F99"/>
+  <dimension ref="A1:F118"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="25.77734375" style="2" customWidth="1"/>
@@ -2183,7 +2195,7 @@
     </row>
     <row r="86" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A86" s="2" t="s">
-        <v>57</v>
+        <v>3</v>
       </c>
       <c r="B86" s="2" t="s">
         <v>24</v>
@@ -2459,8 +2471,390 @@
         <v>0</v>
       </c>
     </row>
+    <row r="100" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A100" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B100" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="C100" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D100" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E100" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="F100" s="2">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="101" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A101" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B101" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="C101" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D101" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="E101" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="F101" s="2">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="102" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A102" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="B102" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="C102" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D102" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="E102" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="F102" s="2">
+        <f>71+50</f>
+        <v>121</v>
+      </c>
+    </row>
+    <row r="103" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A103" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="B103" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="C103" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D103" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E103" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="F103" s="2">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="104" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A104" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B104" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="C104" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D104" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E104" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="F104" s="2">
+        <v>441.5</v>
+      </c>
+    </row>
+    <row r="105" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A105" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B105" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="C105" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D105" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="E105" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="F105" s="2">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="106" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A106" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="B106" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="C106" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D106" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="E106" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="F106" s="2">
+        <f>71+26</f>
+        <v>97</v>
+      </c>
+    </row>
+    <row r="107" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A107" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="B107" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="C107" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D107" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E107" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="F107" s="2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="108" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A108" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B108" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="C108" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D108" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E108" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="F108" s="2">
+        <v>466.5</v>
+      </c>
+    </row>
+    <row r="109" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A109" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B109" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="C109" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D109" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="E109" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="F109" s="2">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="110" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A110" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="B110" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="C110" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D110" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="E110" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="F110" s="2">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="111" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A111" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="B111" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="C111" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D111" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E111" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="F111" s="2">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="112" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A112" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B112" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="C112" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D112" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E112" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="F112" s="2">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="113" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A113" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B113" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="C113" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D113" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="E113" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="F113" s="2">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="114" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A114" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="B114" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="C114" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D114" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="E114" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="F114" s="2">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="115" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A115" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="B115" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="C115" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D115" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E115" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="F115" s="2">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="116" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A116" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B116" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="C116" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D116" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E116" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="F116" s="2">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="117" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A117" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B117" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="C117" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D117" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="E117" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="F117" s="2">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="118" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A118" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="B118" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="C118" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D118" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="E118" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="F118" s="2">
+        <v>71</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:F99" xr:uid="{35372E75-D8AE-4D2B-8467-46A14CD55223}">
+  <autoFilter ref="A1:F118" xr:uid="{35372E75-D8AE-4D2B-8467-46A14CD55223}">
     <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:F99">
       <sortCondition ref="E2:E99"/>
     </sortState>
